--- a/artfynd/A 48921-2025 artfynd.xlsx
+++ b/artfynd/A 48921-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247323</v>
       </c>
       <c r="B2" t="n">
-        <v>99292</v>
+        <v>99299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48921-2025 artfynd.xlsx
+++ b/artfynd/A 48921-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247323</v>
       </c>
       <c r="B2" t="n">
-        <v>99302</v>
+        <v>99307</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48921-2025 artfynd.xlsx
+++ b/artfynd/A 48921-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247323</v>
       </c>
       <c r="B2" t="n">
-        <v>99307</v>
+        <v>99315</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48921-2025 artfynd.xlsx
+++ b/artfynd/A 48921-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247323</v>
       </c>
       <c r="B2" t="n">
-        <v>99315</v>
+        <v>99325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 48921-2025 artfynd.xlsx
+++ b/artfynd/A 48921-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74247323</v>
       </c>
       <c r="B2" t="n">
-        <v>99325</v>
+        <v>99781</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
